--- a/Assets/Excel/活动配置表.xlsx
+++ b/Assets/Excel/活动配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>f_id</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>f_awardIds</t>
+  </si>
+  <si>
+    <t>f_maxPro</t>
   </si>
   <si>
     <t>int</t>
@@ -83,19 +86,22 @@
 （ID,数量）;（ID,数量）...</t>
   </si>
   <si>
+    <t>最大进度</t>
+  </si>
+  <si>
     <t>星轨启程</t>
   </si>
   <si>
     <t>当星辰在虚空中点亮第一道轨迹，传奇便已开始书写。这不是普通的馈赠，而是对先驱者的庄严加冕。真正的旅程始于足下，而卓越始于起点。这个礼遇不仅是一份资源，更是对您选择这个世界的回响。它将在您的成长曲线上绘制第一条优雅的上升轨迹。</t>
   </si>
   <si>
-    <t>Activity_Pic_07</t>
+    <t>OrbitalDeparture</t>
   </si>
   <si>
     <t>OrbitalDepartureActivityUI</t>
   </si>
   <si>
-    <t>10001,1000;10002,10</t>
+    <t>10001,1000;10002,10;10003,1</t>
   </si>
   <si>
     <t>余烬圣典</t>
@@ -104,7 +110,7 @@
     <t>当文明的余温尚未在时空中冷却，英雄便从灰烬中拾起未完的篇章。这是献给真正战士的试炼剧场。这里不考验蛮力，而检验智慧、勇气与对战斗艺术的深刻理解。这里没有永恒的胜利，只有不断被打破的极限它是战斗美学的展览馆，是战术思维的试验场，更是每一位参与者为自己加冕的永恒瞬间。</t>
   </si>
   <si>
-    <t>Activity_Pic_02</t>
+    <t>EmbersCanon</t>
   </si>
   <si>
     <t>EmbersCanonActivityUI</t>
@@ -1077,8 +1083,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="19.25" customWidth="1"/>
@@ -1087,9 +1093,11 @@
     <col min="5" max="5" width="36.625" customWidth="1"/>
     <col min="6" max="6" width="21.6333333333333" customWidth="1"/>
     <col min="7" max="7" width="29.2333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.5416666666667" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1111,102 +1119,117 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="24" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="69" customHeight="1" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="69" customHeight="1" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="86" customHeight="1" spans="1:7">
+    <row r="5" s="2" customFormat="1" ht="86" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>-1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="106" customHeight="1" spans="1:7">
+    <row r="6" s="3" customFormat="1" ht="106" customHeight="1" spans="1:8">
       <c r="A6" s="3">
         <v>1002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>21</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/活动配置表.xlsx
+++ b/Assets/Excel/活动配置表.xlsx
@@ -1229,7 +1229,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
